--- a/results/04_final_refined_daily_hydroclimate_data/702/Daily_temperature_and_precipitation_station_702.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Daily_temperature_and_precipitation_station_702.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Year</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>Year_Num</t>
-  </si>
-  <si>
-    <t>Condition 1</t>
   </si>
 </sst>
 </file>
@@ -514,7 +511,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="E2">
         <v>9.199999999999999</v>
@@ -522,6 +519,12 @@
       <c r="F2">
         <v>18.5</v>
       </c>
+      <c r="H2">
+        <v>9.9</v>
+      </c>
+      <c r="J2">
+        <v>22.1</v>
+      </c>
       <c r="R2" s="2">
         <v>23408</v>
       </c>
@@ -551,6 +554,15 @@
       <c r="F3">
         <v>19.2</v>
       </c>
+      <c r="H3">
+        <v>12.3</v>
+      </c>
+      <c r="J3">
+        <v>19.5</v>
+      </c>
+      <c r="M3">
+        <v>16.1</v>
+      </c>
       <c r="R3" s="2">
         <v>23409</v>
       </c>
@@ -575,10 +587,19 @@
         <v>25.9</v>
       </c>
       <c r="E4">
-        <v>10.9</v>
+        <v>7.9</v>
       </c>
       <c r="F4">
-        <v>18.4</v>
+        <v>16.9</v>
+      </c>
+      <c r="H4">
+        <v>11.1</v>
+      </c>
+      <c r="J4">
+        <v>15.8</v>
+      </c>
+      <c r="K4">
+        <v>11</v>
       </c>
       <c r="R4" s="2">
         <v>23410</v>
@@ -609,6 +630,12 @@
       <c r="F5">
         <v>17.4</v>
       </c>
+      <c r="H5">
+        <v>13.2</v>
+      </c>
+      <c r="J5">
+        <v>18.9</v>
+      </c>
       <c r="R5" s="2">
         <v>23411</v>
       </c>
@@ -630,13 +657,19 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>27.3</v>
+        <v>26.3</v>
       </c>
       <c r="E6">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="F6">
-        <v>18.9</v>
+        <v>18.3</v>
+      </c>
+      <c r="H6">
+        <v>10.8</v>
+      </c>
+      <c r="J6">
+        <v>18.7</v>
       </c>
       <c r="R6" s="2">
         <v>23412</v>
@@ -658,6 +691,21 @@
       <c r="C7">
         <v>6</v>
       </c>
+      <c r="D7">
+        <v>27.3</v>
+      </c>
+      <c r="E7">
+        <v>10.7</v>
+      </c>
+      <c r="F7">
+        <v>19</v>
+      </c>
+      <c r="J7">
+        <v>22.1</v>
+      </c>
+      <c r="L7">
+        <v>17.1</v>
+      </c>
       <c r="R7" s="2">
         <v>23413</v>
       </c>
@@ -678,6 +726,21 @@
       <c r="C8">
         <v>7</v>
       </c>
+      <c r="D8">
+        <v>25.9</v>
+      </c>
+      <c r="E8">
+        <v>10.9</v>
+      </c>
+      <c r="F8">
+        <v>18.4</v>
+      </c>
+      <c r="J8">
+        <v>21.3</v>
+      </c>
+      <c r="L8">
+        <v>15.5</v>
+      </c>
       <c r="R8" s="2">
         <v>23414</v>
       </c>
@@ -707,6 +770,15 @@
       <c r="F9">
         <v>18.2</v>
       </c>
+      <c r="J9">
+        <v>19.6</v>
+      </c>
+      <c r="L9">
+        <v>17.3</v>
+      </c>
+      <c r="M9">
+        <v>16.8</v>
+      </c>
       <c r="R9" s="2">
         <v>23415</v>
       </c>
@@ -727,6 +799,21 @@
       <c r="C10">
         <v>9</v>
       </c>
+      <c r="D10">
+        <v>23.6</v>
+      </c>
+      <c r="E10">
+        <v>13.1</v>
+      </c>
+      <c r="F10">
+        <v>18.2</v>
+      </c>
+      <c r="J10">
+        <v>14.5</v>
+      </c>
+      <c r="L10">
+        <v>14.7</v>
+      </c>
       <c r="R10" s="2">
         <v>23416</v>
       </c>
@@ -751,10 +838,19 @@
         <v>26</v>
       </c>
       <c r="E11">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="F11">
-        <v>18.5</v>
+        <v>18.15</v>
+      </c>
+      <c r="J11">
+        <v>20.7</v>
+      </c>
+      <c r="L11">
+        <v>17.6</v>
+      </c>
+      <c r="M11">
+        <v>14.4</v>
       </c>
       <c r="R11" s="2">
         <v>23417</v>
@@ -785,14 +881,17 @@
       <c r="F12">
         <v>18.4</v>
       </c>
+      <c r="H12">
+        <v>14.7</v>
+      </c>
       <c r="I12">
         <v>25.8</v>
       </c>
       <c r="J12">
         <v>21</v>
       </c>
-      <c r="L12">
-        <v>17.3</v>
+      <c r="K12">
+        <v>14.5</v>
       </c>
       <c r="R12" s="2">
         <v>23418</v>
@@ -823,14 +922,17 @@
       <c r="F13">
         <v>19.3</v>
       </c>
+      <c r="H13">
+        <v>11.2</v>
+      </c>
       <c r="I13">
         <v>25.9</v>
       </c>
       <c r="J13">
         <v>21.2</v>
       </c>
-      <c r="L13">
-        <v>18</v>
+      <c r="M13">
+        <v>16.4</v>
       </c>
       <c r="R13" s="2">
         <v>23419</v>
@@ -861,15 +963,15 @@
       <c r="F14">
         <v>19.3</v>
       </c>
+      <c r="H14">
+        <v>11.2</v>
+      </c>
       <c r="I14">
         <v>28</v>
       </c>
       <c r="J14">
         <v>22.2</v>
       </c>
-      <c r="L14">
-        <v>18.9</v>
-      </c>
       <c r="R14" s="2">
         <v>23420</v>
       </c>
@@ -891,13 +993,10 @@
         <v>14</v>
       </c>
       <c r="D15">
-        <v>24.5</v>
-      </c>
-      <c r="E15">
-        <v>12.6</v>
-      </c>
-      <c r="F15">
-        <v>18.9</v>
+        <v>24.8</v>
+      </c>
+      <c r="H15">
+        <v>13.1</v>
       </c>
       <c r="I15">
         <v>25.6</v>
@@ -905,9 +1004,6 @@
       <c r="J15">
         <v>19.8</v>
       </c>
-      <c r="L15">
-        <v>18.2</v>
-      </c>
       <c r="R15" s="2">
         <v>23421</v>
       </c>
@@ -931,11 +1027,8 @@
       <c r="D16">
         <v>25.2</v>
       </c>
-      <c r="E16">
-        <v>12.2</v>
-      </c>
-      <c r="F16">
-        <v>18.7</v>
+      <c r="H16">
+        <v>12.3</v>
       </c>
       <c r="I16">
         <v>23.6</v>
@@ -943,9 +1036,6 @@
       <c r="J16">
         <v>22.5</v>
       </c>
-      <c r="L16">
-        <v>16.2</v>
-      </c>
       <c r="R16" s="2">
         <v>23422</v>
       </c>
@@ -966,18 +1056,30 @@
       <c r="C17">
         <v>16</v>
       </c>
+      <c r="D17">
+        <v>25.9</v>
+      </c>
+      <c r="E17">
+        <v>9.699999999999999</v>
+      </c>
       <c r="F17">
         <v>17.8</v>
       </c>
+      <c r="H17">
+        <v>10.7</v>
+      </c>
+      <c r="I17">
+        <v>24.7</v>
+      </c>
       <c r="J17">
         <v>21.3</v>
       </c>
+      <c r="L17">
+        <v>17.2</v>
+      </c>
       <c r="M17">
         <v>14.8</v>
       </c>
-      <c r="N17" t="s">
-        <v>20</v>
-      </c>
       <c r="R17" s="2">
         <v>23423</v>
       </c>
@@ -1007,9 +1109,21 @@
       <c r="F18">
         <v>17</v>
       </c>
+      <c r="H18">
+        <v>10.4</v>
+      </c>
+      <c r="I18">
+        <v>21</v>
+      </c>
       <c r="J18">
         <v>21.6</v>
       </c>
+      <c r="L18">
+        <v>16.2</v>
+      </c>
+      <c r="M18">
+        <v>15.5</v>
+      </c>
       <c r="R18" s="2">
         <v>23424</v>
       </c>
@@ -1030,17 +1144,29 @@
       <c r="C19">
         <v>18</v>
       </c>
+      <c r="D19">
+        <v>25.7</v>
+      </c>
       <c r="E19">
-        <v>17.1</v>
+        <v>10.5</v>
       </c>
       <c r="F19">
         <v>18.1</v>
       </c>
+      <c r="H19">
+        <v>12.4</v>
+      </c>
+      <c r="I19">
+        <v>17.6</v>
+      </c>
       <c r="J19">
         <v>17.4</v>
       </c>
-      <c r="N19" t="s">
-        <v>20</v>
+      <c r="L19">
+        <v>16</v>
+      </c>
+      <c r="M19">
+        <v>16.7</v>
       </c>
       <c r="R19" s="2">
         <v>23425</v>
@@ -1066,13 +1192,28 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F20">
         <v>19.3</v>
       </c>
+      <c r="H20">
+        <v>13.5</v>
+      </c>
+      <c r="I20">
+        <v>22.9</v>
+      </c>
       <c r="J20">
-        <v>16.9</v>
+        <v>16.4</v>
+      </c>
+      <c r="K20">
+        <v>13.3</v>
+      </c>
+      <c r="L20">
+        <v>18.6</v>
+      </c>
+      <c r="M20">
+        <v>15.5</v>
       </c>
       <c r="R20" s="2">
         <v>23426</v>
@@ -1095,17 +1236,29 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>28.3</v>
+        <v>28.8</v>
       </c>
       <c r="E21">
-        <v>10.7</v>
+        <v>10.1</v>
       </c>
       <c r="F21">
         <v>19.5</v>
       </c>
+      <c r="H21">
+        <v>10.9</v>
+      </c>
+      <c r="I21">
+        <v>27</v>
+      </c>
       <c r="J21">
         <v>22.8</v>
       </c>
+      <c r="L21">
+        <v>15</v>
+      </c>
+      <c r="M21">
+        <v>17.3</v>
+      </c>
       <c r="R21" s="2">
         <v>23427</v>
       </c>
@@ -1135,12 +1288,18 @@
       <c r="F22">
         <v>19</v>
       </c>
-      <c r="H22">
-        <v>10.5</v>
+      <c r="I22">
+        <v>26.46</v>
+      </c>
+      <c r="K22">
+        <v>10.2</v>
       </c>
       <c r="L22">
         <v>18.2</v>
       </c>
+      <c r="M22">
+        <v>17.6</v>
+      </c>
       <c r="R22" s="2">
         <v>23428</v>
       </c>
@@ -1170,12 +1329,18 @@
       <c r="F23">
         <v>18.5</v>
       </c>
-      <c r="H23">
-        <v>19.9</v>
+      <c r="I23">
+        <v>20.3</v>
+      </c>
+      <c r="K23">
+        <v>14.2</v>
       </c>
       <c r="L23">
         <v>17.8</v>
       </c>
+      <c r="M23">
+        <v>17.9</v>
+      </c>
       <c r="R23" s="2">
         <v>23429</v>
       </c>
@@ -1205,12 +1370,18 @@
       <c r="F24">
         <v>19</v>
       </c>
-      <c r="H24">
-        <v>12</v>
+      <c r="I24">
+        <v>21.8</v>
+      </c>
+      <c r="K24">
+        <v>15.9</v>
       </c>
       <c r="L24">
         <v>18.1</v>
       </c>
+      <c r="M24">
+        <v>16.8</v>
+      </c>
       <c r="R24" s="2">
         <v>23430</v>
       </c>
@@ -1243,9 +1414,18 @@
       <c r="H25">
         <v>13</v>
       </c>
+      <c r="I25">
+        <v>23.8</v>
+      </c>
+      <c r="K25">
+        <v>12.9</v>
+      </c>
       <c r="L25">
         <v>17.6</v>
       </c>
+      <c r="M25">
+        <v>16.7</v>
+      </c>
       <c r="R25" s="2">
         <v>23431</v>
       </c>
@@ -1270,20 +1450,23 @@
         <v>26.3</v>
       </c>
       <c r="E26">
-        <v>10.54</v>
+        <v>10.9</v>
       </c>
       <c r="F26">
-        <v>18.2</v>
-      </c>
-      <c r="H26">
-        <v>10.3</v>
+        <v>18.6</v>
+      </c>
+      <c r="I26">
+        <v>23.5</v>
       </c>
       <c r="K26">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="L26">
         <v>17.1</v>
       </c>
+      <c r="M26">
+        <v>14.6</v>
+      </c>
       <c r="R26" s="2">
         <v>23432</v>
       </c>
@@ -1305,19 +1488,19 @@
         <v>26</v>
       </c>
       <c r="D27">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="E27">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F27">
         <v>18.9</v>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>15.7</v>
+      <c r="I27">
+        <v>26.6</v>
+      </c>
+      <c r="K27">
+        <v>12.5</v>
       </c>
       <c r="R27" s="2">
         <v>23433</v>
@@ -1340,7 +1523,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="E28">
         <v>10.7</v>
@@ -1348,11 +1531,11 @@
       <c r="F28">
         <v>18.9</v>
       </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>18.15</v>
+      <c r="I28">
+        <v>22</v>
+      </c>
+      <c r="K28">
+        <v>10.3</v>
       </c>
       <c r="R28" s="2">
         <v>23434</v>
@@ -1375,19 +1558,13 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>28.4</v>
-      </c>
-      <c r="E29">
+        <v>28.94</v>
+      </c>
+      <c r="I29">
+        <v>23.9</v>
+      </c>
+      <c r="K29">
         <v>8.6</v>
-      </c>
-      <c r="F29">
-        <v>18.5</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>16.3</v>
       </c>
       <c r="R29" s="2">
         <v>23435</v>
@@ -1412,17 +1589,14 @@
       <c r="D30">
         <v>27.2</v>
       </c>
-      <c r="E30">
-        <v>11.4</v>
-      </c>
       <c r="F30">
         <v>19.3</v>
       </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>16.3</v>
+      <c r="I30">
+        <v>26.6</v>
+      </c>
+      <c r="K30">
+        <v>11.1</v>
       </c>
       <c r="R30" s="2">
         <v>23436</v>
@@ -1453,12 +1627,6 @@
       <c r="F31">
         <v>19.9</v>
       </c>
-      <c r="J31">
-        <v>17.8</v>
-      </c>
-      <c r="L31">
-        <v>17.3</v>
-      </c>
       <c r="M31">
         <v>17</v>
       </c>
@@ -1483,25 +1651,22 @@
         <v>2</v>
       </c>
       <c r="D32">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="E32">
-        <v>15.1</v>
+        <v>14</v>
       </c>
       <c r="F32">
         <v>20.3</v>
       </c>
       <c r="I32">
-        <v>21.1</v>
-      </c>
-      <c r="J32">
-        <v>20.3</v>
+        <v>21.3</v>
       </c>
       <c r="L32">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="M32">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="R32" s="2">
         <v>23469</v>
@@ -1524,19 +1689,13 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>24.9</v>
+        <v>24.4</v>
       </c>
       <c r="E33">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="F33">
-        <v>19.7</v>
-      </c>
-      <c r="J33">
-        <v>18.8</v>
-      </c>
-      <c r="L33">
-        <v>17.9</v>
+        <v>19.3</v>
       </c>
       <c r="M33">
         <v>18</v>
@@ -1570,12 +1729,6 @@
       <c r="F34">
         <v>19.9</v>
       </c>
-      <c r="J34">
-        <v>18.8</v>
-      </c>
-      <c r="L34">
-        <v>17.2</v>
-      </c>
       <c r="M34">
         <v>17</v>
       </c>
@@ -1608,15 +1761,6 @@
       <c r="F35">
         <v>19.6</v>
       </c>
-      <c r="I35">
-        <v>22.2</v>
-      </c>
-      <c r="J35">
-        <v>19.8</v>
-      </c>
-      <c r="L35">
-        <v>17.1</v>
-      </c>
       <c r="M35">
         <v>17.8</v>
       </c>
@@ -1640,8 +1784,20 @@
       <c r="C36">
         <v>6</v>
       </c>
-      <c r="J36">
-        <v>18.86</v>
+      <c r="D36">
+        <v>23.4</v>
+      </c>
+      <c r="E36">
+        <v>16.1</v>
+      </c>
+      <c r="F36">
+        <v>18.7</v>
+      </c>
+      <c r="H36">
+        <v>12.28</v>
+      </c>
+      <c r="M36">
+        <v>18.1</v>
       </c>
       <c r="R36" s="2">
         <v>23473</v>
@@ -1672,8 +1828,11 @@
       <c r="F37">
         <v>19.8</v>
       </c>
-      <c r="J37">
-        <v>21.2</v>
+      <c r="H37">
+        <v>19.3</v>
+      </c>
+      <c r="M37">
+        <v>19.3</v>
       </c>
       <c r="R37" s="2">
         <v>23474</v>
@@ -1695,8 +1854,20 @@
       <c r="C38">
         <v>8</v>
       </c>
-      <c r="J38">
-        <v>20.8</v>
+      <c r="D38">
+        <v>24.6</v>
+      </c>
+      <c r="E38">
+        <v>11.6</v>
+      </c>
+      <c r="F38">
+        <v>18.1</v>
+      </c>
+      <c r="H38">
+        <v>11.2</v>
+      </c>
+      <c r="M38">
+        <v>17.8</v>
       </c>
       <c r="R38" s="2">
         <v>23475</v>
@@ -1722,13 +1893,16 @@
         <v>26.8</v>
       </c>
       <c r="E39">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="F39">
         <v>19.6</v>
       </c>
-      <c r="J39">
-        <v>20.6</v>
+      <c r="H39">
+        <v>12.5</v>
+      </c>
+      <c r="M39">
+        <v>18.4</v>
       </c>
       <c r="R39" s="2">
         <v>23476</v>
@@ -1751,7 +1925,7 @@
         <v>10</v>
       </c>
       <c r="D40">
-        <v>27.5</v>
+        <v>26.7</v>
       </c>
       <c r="E40">
         <v>14.1</v>
@@ -1760,13 +1934,16 @@
         <v>20.8</v>
       </c>
       <c r="H40">
-        <v>17</v>
-      </c>
-      <c r="J40">
-        <v>19.2</v>
-      </c>
-      <c r="K40">
-        <v>16.5</v>
+        <v>14.9</v>
+      </c>
+      <c r="I40">
+        <v>25.7</v>
+      </c>
+      <c r="L40">
+        <v>13.9</v>
+      </c>
+      <c r="M40">
+        <v>17.3</v>
       </c>
       <c r="R40" s="2">
         <v>23477</v>
@@ -1826,11 +2003,23 @@
       <c r="C42">
         <v>12</v>
       </c>
+      <c r="D42">
+        <v>25.6</v>
+      </c>
+      <c r="E42">
+        <v>13</v>
+      </c>
+      <c r="F42">
+        <v>19.4</v>
+      </c>
+      <c r="J42">
+        <v>19.4</v>
+      </c>
       <c r="L42">
         <v>18.2</v>
       </c>
       <c r="M42">
-        <v>17.5</v>
+        <v>16.6</v>
       </c>
       <c r="R42" s="2">
         <v>23479</v>
@@ -1852,6 +2041,15 @@
       <c r="C43">
         <v>13</v>
       </c>
+      <c r="D43">
+        <v>27.1</v>
+      </c>
+      <c r="E43">
+        <v>12.54</v>
+      </c>
+      <c r="F43">
+        <v>19.8</v>
+      </c>
       <c r="L43">
         <v>17.5</v>
       </c>
@@ -1879,7 +2077,7 @@
         <v>14</v>
       </c>
       <c r="D44">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="E44">
         <v>14.1</v>
@@ -1888,10 +2086,10 @@
         <v>19.8</v>
       </c>
       <c r="L44">
-        <v>18.9</v>
+        <v>18.1</v>
       </c>
       <c r="M44">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
       <c r="R44" s="2">
         <v>23481</v>
@@ -1913,8 +2111,17 @@
       <c r="C45">
         <v>15</v>
       </c>
+      <c r="D45">
+        <v>25.8</v>
+      </c>
+      <c r="E45">
+        <v>13.2</v>
+      </c>
+      <c r="F45">
+        <v>19.5</v>
+      </c>
       <c r="L45">
-        <v>18.54</v>
+        <v>18.7</v>
       </c>
       <c r="M45">
         <v>18</v>
@@ -1939,8 +2146,26 @@
       <c r="C46">
         <v>16</v>
       </c>
+      <c r="D46">
+        <v>23.1</v>
+      </c>
+      <c r="E46">
+        <v>15.5</v>
+      </c>
+      <c r="F46">
+        <v>19.3</v>
+      </c>
+      <c r="H46">
+        <v>16.9</v>
+      </c>
       <c r="I46">
-        <v>18.4</v>
+        <v>18.9</v>
+      </c>
+      <c r="K46">
+        <v>16.5</v>
+      </c>
+      <c r="M46">
+        <v>17</v>
       </c>
       <c r="R46" s="2">
         <v>23483</v>
@@ -1963,10 +2188,10 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="E47">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="F47">
         <v>18.9</v>
@@ -1974,6 +2199,9 @@
       <c r="I47">
         <v>18</v>
       </c>
+      <c r="M47">
+        <v>15.3</v>
+      </c>
       <c r="R47" s="2">
         <v>23484</v>
       </c>
@@ -2006,6 +2234,9 @@
       <c r="I48">
         <v>19.8</v>
       </c>
+      <c r="M48">
+        <v>17.6</v>
+      </c>
       <c r="R48" s="2">
         <v>23485</v>
       </c>
@@ -2033,7 +2264,7 @@
         <v>13.8</v>
       </c>
       <c r="F49">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="I49">
         <v>19.6</v>
@@ -2064,9 +2295,21 @@
       <c r="C50">
         <v>20</v>
       </c>
+      <c r="D50">
+        <v>23.7</v>
+      </c>
+      <c r="E50">
+        <v>13.3</v>
+      </c>
+      <c r="F50">
+        <v>18.5</v>
+      </c>
       <c r="I50">
         <v>23.6</v>
       </c>
+      <c r="M50">
+        <v>15.5</v>
+      </c>
       <c r="R50" s="2">
         <v>23487</v>
       </c>
@@ -2087,15 +2330,9 @@
       <c r="C51">
         <v>21</v>
       </c>
-      <c r="I51">
-        <v>13</v>
-      </c>
       <c r="J51">
         <v>16.6</v>
       </c>
-      <c r="L51">
-        <v>19.8</v>
-      </c>
       <c r="M51">
         <v>16.2</v>
       </c>
@@ -2128,15 +2365,9 @@
       <c r="F52">
         <v>18.7</v>
       </c>
-      <c r="I52">
-        <v>21.2</v>
-      </c>
       <c r="J52">
         <v>17.8</v>
       </c>
-      <c r="L52">
-        <v>18.4</v>
-      </c>
       <c r="M52">
         <v>16.5</v>
       </c>
@@ -2160,15 +2391,9 @@
       <c r="C53">
         <v>23</v>
       </c>
-      <c r="I53">
-        <v>19.6</v>
-      </c>
       <c r="J53">
         <v>16.9</v>
       </c>
-      <c r="L53">
-        <v>15.8</v>
-      </c>
       <c r="M53">
         <v>15.2</v>
       </c>
@@ -2196,20 +2421,14 @@
         <v>24.1</v>
       </c>
       <c r="E54">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="F54">
         <v>18.1</v>
       </c>
-      <c r="I54">
-        <v>23.9</v>
-      </c>
       <c r="J54">
         <v>18.9</v>
       </c>
-      <c r="L54">
-        <v>18.3</v>
-      </c>
       <c r="M54">
         <v>16.5</v>
       </c>
@@ -2242,15 +2461,9 @@
       <c r="F55">
         <v>19.5</v>
       </c>
-      <c r="I55">
-        <v>24</v>
-      </c>
       <c r="J55">
         <v>20.8</v>
       </c>
-      <c r="L55">
-        <v>17.6</v>
-      </c>
       <c r="M55">
         <v>17.2</v>
       </c>
@@ -2275,19 +2488,25 @@
         <v>26</v>
       </c>
       <c r="D56">
-        <v>25.9</v>
+        <v>25.1</v>
       </c>
       <c r="E56">
         <v>11.1</v>
       </c>
       <c r="F56">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="H56">
-        <v>11.1</v>
+        <v>11.3</v>
+      </c>
+      <c r="I56">
+        <v>24.8</v>
       </c>
       <c r="K56">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
+      </c>
+      <c r="M56">
+        <v>16.5</v>
       </c>
       <c r="R56" s="2">
         <v>23493</v>
@@ -2310,14 +2529,20 @@
         <v>27</v>
       </c>
       <c r="D57">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="E57">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F57">
         <v>17.9</v>
       </c>
+      <c r="I57">
+        <v>25.4</v>
+      </c>
+      <c r="M57">
+        <v>17.3</v>
+      </c>
       <c r="R57" s="2">
         <v>23494</v>
       </c>
@@ -2342,10 +2567,16 @@
         <v>26.2</v>
       </c>
       <c r="E58">
-        <v>18</v>
-      </c>
-      <c r="P58" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="F58">
+        <v>18.1</v>
+      </c>
+      <c r="I58">
+        <v>25.2</v>
+      </c>
+      <c r="M58">
+        <v>16.2</v>
       </c>
       <c r="R58" s="2">
         <v>23495</v>
@@ -2367,20 +2598,14 @@
       <c r="C59">
         <v>29</v>
       </c>
-      <c r="D59">
-        <v>26.9</v>
-      </c>
-      <c r="E59">
-        <v>10.4</v>
-      </c>
-      <c r="F59">
-        <v>18.6</v>
-      </c>
       <c r="I59">
-        <v>26.3</v>
+        <v>26.7</v>
       </c>
       <c r="L59">
-        <v>14.8</v>
+        <v>18.2</v>
+      </c>
+      <c r="M59">
+        <v>16.8</v>
       </c>
       <c r="R59" s="2">
         <v>23496</v>
@@ -2403,10 +2628,19 @@
         <v>30</v>
       </c>
       <c r="D60">
-        <v>26.1</v>
+        <v>26.2</v>
+      </c>
+      <c r="E60">
+        <v>12.5</v>
       </c>
       <c r="F60">
         <v>19.2</v>
+      </c>
+      <c r="I60">
+        <v>24.8</v>
+      </c>
+      <c r="M60">
+        <v>16</v>
       </c>
       <c r="R60" s="2">
         <v>23497</v>

--- a/results/04_final_refined_daily_hydroclimate_data/702/Daily_temperature_and_precipitation_station_702.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Daily_temperature_and_precipitation_station_702.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Year</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Year_Num</t>
+  </si>
+  <si>
+    <t>Condition 1</t>
   </si>
 </sst>
 </file>
@@ -519,12 +522,24 @@
       <c r="F2">
         <v>18.5</v>
       </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
       <c r="H2">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I2">
+        <v>25.8</v>
       </c>
       <c r="J2">
         <v>22.1</v>
       </c>
+      <c r="K2">
+        <v>9.1</v>
+      </c>
+      <c r="L2">
+        <v>12.1</v>
+      </c>
       <c r="R2" s="2">
         <v>23408</v>
       </c>
@@ -554,14 +569,23 @@
       <c r="F3">
         <v>19.2</v>
       </c>
+      <c r="G3">
+        <v>1.2</v>
+      </c>
       <c r="H3">
         <v>12.3</v>
       </c>
+      <c r="I3">
+        <v>19.6</v>
+      </c>
       <c r="J3">
         <v>19.5</v>
       </c>
-      <c r="M3">
-        <v>16.1</v>
+      <c r="K3">
+        <v>11.4</v>
+      </c>
+      <c r="L3">
+        <v>18.6</v>
       </c>
       <c r="R3" s="2">
         <v>23409</v>
@@ -587,20 +611,32 @@
         <v>25.9</v>
       </c>
       <c r="E4">
-        <v>7.9</v>
+        <v>10.9</v>
       </c>
       <c r="F4">
-        <v>16.9</v>
+        <v>18.4</v>
+      </c>
+      <c r="G4">
+        <v>6.5</v>
       </c>
       <c r="H4">
         <v>11.1</v>
       </c>
+      <c r="I4">
+        <v>15.4</v>
+      </c>
       <c r="J4">
         <v>15.8</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
+      <c r="L4">
+        <v>14.7</v>
+      </c>
+      <c r="M4">
+        <v>15.1</v>
+      </c>
       <c r="R4" s="2">
         <v>23410</v>
       </c>
@@ -630,12 +666,24 @@
       <c r="F5">
         <v>17.4</v>
       </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
       <c r="H5">
         <v>13.2</v>
       </c>
+      <c r="I5">
+        <v>19.3</v>
+      </c>
       <c r="J5">
         <v>18.9</v>
       </c>
+      <c r="K5">
+        <v>13.1</v>
+      </c>
+      <c r="L5">
+        <v>16.8</v>
+      </c>
       <c r="R5" s="2">
         <v>23411</v>
       </c>
@@ -660,17 +708,29 @@
         <v>26.3</v>
       </c>
       <c r="E6">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="F6">
-        <v>18.3</v>
+        <v>18.4</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
       </c>
       <c r="H6">
         <v>10.8</v>
       </c>
+      <c r="I6">
+        <v>21.4</v>
+      </c>
       <c r="J6">
         <v>18.7</v>
       </c>
+      <c r="K6">
+        <v>10.6</v>
+      </c>
+      <c r="L6">
+        <v>18.4</v>
+      </c>
       <c r="R6" s="2">
         <v>23412</v>
       </c>
@@ -700,11 +760,17 @@
       <c r="F7">
         <v>19</v>
       </c>
+      <c r="I7">
+        <v>26.3</v>
+      </c>
       <c r="J7">
         <v>22.1</v>
       </c>
       <c r="L7">
-        <v>17.1</v>
+        <v>12.4</v>
+      </c>
+      <c r="M7">
+        <v>17.6</v>
       </c>
       <c r="R7" s="2">
         <v>23413</v>
@@ -735,12 +801,18 @@
       <c r="F8">
         <v>18.4</v>
       </c>
+      <c r="I8">
+        <v>25.4</v>
+      </c>
       <c r="J8">
         <v>21.3</v>
       </c>
       <c r="L8">
         <v>15.5</v>
       </c>
+      <c r="M8">
+        <v>14.7</v>
+      </c>
       <c r="R8" s="2">
         <v>23414</v>
       </c>
@@ -762,13 +834,16 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="E9">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="F9">
-        <v>18.2</v>
+        <v>18.3</v>
+      </c>
+      <c r="I9">
+        <v>18.9</v>
       </c>
       <c r="J9">
         <v>19.6</v>
@@ -800,13 +875,16 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="E10">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>18.2</v>
+        <v>18.3</v>
+      </c>
+      <c r="I10">
+        <v>14.9</v>
       </c>
       <c r="J10">
         <v>14.5</v>
@@ -814,6 +892,9 @@
       <c r="L10">
         <v>14.7</v>
       </c>
+      <c r="M10">
+        <v>15.2</v>
+      </c>
       <c r="R10" s="2">
         <v>23416</v>
       </c>
@@ -838,16 +919,19 @@
         <v>26</v>
       </c>
       <c r="E11">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="F11">
-        <v>18.15</v>
+        <v>18.5</v>
+      </c>
+      <c r="I11">
+        <v>25.5</v>
       </c>
       <c r="J11">
         <v>20.7</v>
       </c>
       <c r="L11">
-        <v>17.6</v>
+        <v>13.7</v>
       </c>
       <c r="M11">
         <v>14.4</v>
@@ -879,7 +963,10 @@
         <v>10.9</v>
       </c>
       <c r="F12">
-        <v>18.4</v>
+        <v>18.7</v>
+      </c>
+      <c r="G12">
+        <v>0.1</v>
       </c>
       <c r="H12">
         <v>14.7</v>
@@ -893,6 +980,12 @@
       <c r="K12">
         <v>14.5</v>
       </c>
+      <c r="L12">
+        <v>13.4</v>
+      </c>
+      <c r="M12">
+        <v>15.5</v>
+      </c>
       <c r="R12" s="2">
         <v>23418</v>
       </c>
@@ -922,6 +1015,9 @@
       <c r="F13">
         <v>19.3</v>
       </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
       <c r="H13">
         <v>11.2</v>
       </c>
@@ -931,6 +1027,12 @@
       <c r="J13">
         <v>21.2</v>
       </c>
+      <c r="K13">
+        <v>11</v>
+      </c>
+      <c r="L13">
+        <v>14.2</v>
+      </c>
       <c r="M13">
         <v>16.4</v>
       </c>
@@ -963,6 +1065,9 @@
       <c r="F14">
         <v>19.3</v>
       </c>
+      <c r="G14">
+        <v>0.2</v>
+      </c>
       <c r="H14">
         <v>11.2</v>
       </c>
@@ -972,6 +1077,15 @@
       <c r="J14">
         <v>22.2</v>
       </c>
+      <c r="K14">
+        <v>11</v>
+      </c>
+      <c r="L14">
+        <v>13.3</v>
+      </c>
+      <c r="M14">
+        <v>18.4</v>
+      </c>
       <c r="R14" s="2">
         <v>23420</v>
       </c>
@@ -995,6 +1109,15 @@
       <c r="D15">
         <v>24.8</v>
       </c>
+      <c r="E15">
+        <v>12.7</v>
+      </c>
+      <c r="F15">
+        <v>18.7</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
       <c r="H15">
         <v>13.1</v>
       </c>
@@ -1004,6 +1127,15 @@
       <c r="J15">
         <v>19.8</v>
       </c>
+      <c r="K15">
+        <v>13</v>
+      </c>
+      <c r="L15">
+        <v>14.8</v>
+      </c>
+      <c r="M15">
+        <v>17.5</v>
+      </c>
       <c r="R15" s="2">
         <v>23421</v>
       </c>
@@ -1027,6 +1159,15 @@
       <c r="D16">
         <v>25.2</v>
       </c>
+      <c r="E16">
+        <v>12.1</v>
+      </c>
+      <c r="F16">
+        <v>18.7</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
       <c r="H16">
         <v>12.3</v>
       </c>
@@ -1036,6 +1177,15 @@
       <c r="J16">
         <v>22.5</v>
       </c>
+      <c r="K16">
+        <v>12.2</v>
+      </c>
+      <c r="L16">
+        <v>12.4</v>
+      </c>
+      <c r="M16">
+        <v>15.6</v>
+      </c>
       <c r="R16" s="2">
         <v>23422</v>
       </c>
@@ -1065,8 +1215,11 @@
       <c r="F17">
         <v>17.8</v>
       </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
       <c r="H17">
-        <v>10.7</v>
+        <v>10.1</v>
       </c>
       <c r="I17">
         <v>24.7</v>
@@ -1074,6 +1227,9 @@
       <c r="J17">
         <v>21.3</v>
       </c>
+      <c r="K17">
+        <v>9.9</v>
+      </c>
       <c r="L17">
         <v>17.2</v>
       </c>
@@ -1109,6 +1265,9 @@
       <c r="F18">
         <v>17</v>
       </c>
+      <c r="G18">
+        <v>0.9</v>
+      </c>
       <c r="H18">
         <v>10.4</v>
       </c>
@@ -1118,12 +1277,12 @@
       <c r="J18">
         <v>21.6</v>
       </c>
+      <c r="K18">
+        <v>10.2</v>
+      </c>
       <c r="L18">
         <v>16.2</v>
       </c>
-      <c r="M18">
-        <v>15.5</v>
-      </c>
       <c r="R18" s="2">
         <v>23424</v>
       </c>
@@ -1145,14 +1304,17 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>25.7</v>
+        <v>25.1</v>
       </c>
       <c r="E19">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="F19">
         <v>18.1</v>
       </c>
+      <c r="G19">
+        <v>7.1</v>
+      </c>
       <c r="H19">
         <v>12.4</v>
       </c>
@@ -1162,12 +1324,12 @@
       <c r="J19">
         <v>17.4</v>
       </c>
+      <c r="K19">
+        <v>12.2</v>
+      </c>
       <c r="L19">
         <v>16</v>
       </c>
-      <c r="M19">
-        <v>16.7</v>
-      </c>
       <c r="R19" s="2">
         <v>23425</v>
       </c>
@@ -1197,8 +1359,11 @@
       <c r="F20">
         <v>19.3</v>
       </c>
+      <c r="G20">
+        <v>5.5</v>
+      </c>
       <c r="H20">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="I20">
         <v>22.9</v>
@@ -1212,9 +1377,6 @@
       <c r="L20">
         <v>18.6</v>
       </c>
-      <c r="M20">
-        <v>15.5</v>
-      </c>
       <c r="R20" s="2">
         <v>23426</v>
       </c>
@@ -1244,6 +1406,9 @@
       <c r="F21">
         <v>19.5</v>
       </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
       <c r="H21">
         <v>10.9</v>
       </c>
@@ -1253,11 +1418,14 @@
       <c r="J21">
         <v>22.8</v>
       </c>
+      <c r="K21">
+        <v>10.5</v>
+      </c>
       <c r="L21">
         <v>15</v>
       </c>
       <c r="M21">
-        <v>17.3</v>
+        <v>14.7</v>
       </c>
       <c r="R21" s="2">
         <v>23427</v>
@@ -1286,10 +1454,16 @@
         <v>10.2</v>
       </c>
       <c r="F22">
-        <v>19</v>
-      </c>
-      <c r="I22">
-        <v>26.46</v>
+        <v>19.1</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>10.5</v>
+      </c>
+      <c r="J22">
+        <v>21.4</v>
       </c>
       <c r="K22">
         <v>10.2</v>
@@ -1329,11 +1503,17 @@
       <c r="F23">
         <v>18.5</v>
       </c>
-      <c r="I23">
-        <v>20.3</v>
+      <c r="G23">
+        <v>6.8</v>
+      </c>
+      <c r="H23">
+        <v>14.9</v>
+      </c>
+      <c r="J23">
+        <v>19.4</v>
       </c>
       <c r="K23">
-        <v>14.2</v>
+        <v>14.7</v>
       </c>
       <c r="L23">
         <v>17.8</v>
@@ -1370,8 +1550,14 @@
       <c r="F24">
         <v>19</v>
       </c>
-      <c r="I24">
-        <v>21.8</v>
+      <c r="G24">
+        <v>1.7</v>
+      </c>
+      <c r="H24">
+        <v>16</v>
+      </c>
+      <c r="J24">
+        <v>18.7</v>
       </c>
       <c r="K24">
         <v>15.9</v>
@@ -1411,11 +1597,14 @@
       <c r="F25">
         <v>19.8</v>
       </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
       <c r="H25">
         <v>13</v>
       </c>
-      <c r="I25">
-        <v>23.8</v>
+      <c r="J25">
+        <v>20.8</v>
       </c>
       <c r="K25">
         <v>12.9</v>
@@ -1450,13 +1639,19 @@
         <v>26.3</v>
       </c>
       <c r="E26">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F26">
-        <v>18.6</v>
-      </c>
-      <c r="I26">
-        <v>23.5</v>
+        <v>18.3</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>10.6</v>
+      </c>
+      <c r="J26">
+        <v>20.6</v>
       </c>
       <c r="K26">
         <v>10.5</v>
@@ -1496,11 +1691,20 @@
       <c r="F27">
         <v>18.9</v>
       </c>
-      <c r="I27">
-        <v>26.6</v>
-      </c>
-      <c r="K27">
-        <v>12.5</v>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>12.7</v>
+      </c>
+      <c r="J27">
+        <v>21.7</v>
+      </c>
+      <c r="L27">
+        <v>18</v>
+      </c>
+      <c r="M27">
+        <v>15.7</v>
       </c>
       <c r="R27" s="2">
         <v>23433</v>
@@ -1531,12 +1735,27 @@
       <c r="F28">
         <v>18.9</v>
       </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>10.6</v>
+      </c>
       <c r="I28">
         <v>22</v>
       </c>
+      <c r="J28">
+        <v>19.7</v>
+      </c>
       <c r="K28">
         <v>10.3</v>
       </c>
+      <c r="L28">
+        <v>16.2</v>
+      </c>
+      <c r="M28">
+        <v>16.8</v>
+      </c>
       <c r="R28" s="2">
         <v>23434</v>
       </c>
@@ -1558,13 +1777,28 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>28.94</v>
-      </c>
-      <c r="I29">
-        <v>23.9</v>
-      </c>
-      <c r="K29">
+        <v>28.4</v>
+      </c>
+      <c r="E29">
         <v>8.6</v>
+      </c>
+      <c r="F29">
+        <v>18.5</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J29">
+        <v>22</v>
+      </c>
+      <c r="L29">
+        <v>17.4</v>
+      </c>
+      <c r="M29">
+        <v>18.5</v>
       </c>
       <c r="R29" s="2">
         <v>23435</v>
@@ -1589,14 +1823,23 @@
       <c r="D30">
         <v>27.2</v>
       </c>
+      <c r="E30">
+        <v>11.4</v>
+      </c>
       <c r="F30">
         <v>19.3</v>
       </c>
-      <c r="I30">
-        <v>26.6</v>
-      </c>
-      <c r="K30">
-        <v>11.1</v>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>11.9</v>
+      </c>
+      <c r="J30">
+        <v>22</v>
+      </c>
+      <c r="L30">
+        <v>17.6</v>
       </c>
       <c r="R30" s="2">
         <v>23436</v>
@@ -1627,6 +1870,21 @@
       <c r="F31">
         <v>19.9</v>
       </c>
+      <c r="H31">
+        <v>16</v>
+      </c>
+      <c r="I31">
+        <v>17.7</v>
+      </c>
+      <c r="J31">
+        <v>17.8</v>
+      </c>
+      <c r="K31">
+        <v>15.9</v>
+      </c>
+      <c r="L31">
+        <v>17.3</v>
+      </c>
       <c r="M31">
         <v>17</v>
       </c>
@@ -1662,8 +1920,14 @@
       <c r="I32">
         <v>21.3</v>
       </c>
+      <c r="J32">
+        <v>20.3</v>
+      </c>
+      <c r="K32">
+        <v>13.9</v>
+      </c>
       <c r="L32">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="M32">
         <v>17.4</v>
@@ -1697,6 +1961,21 @@
       <c r="F33">
         <v>19.3</v>
       </c>
+      <c r="H33">
+        <v>14.3</v>
+      </c>
+      <c r="I33">
+        <v>22.2</v>
+      </c>
+      <c r="J33">
+        <v>18.8</v>
+      </c>
+      <c r="K33">
+        <v>14.2</v>
+      </c>
+      <c r="L33">
+        <v>17.9</v>
+      </c>
       <c r="M33">
         <v>18</v>
       </c>
@@ -1729,8 +2008,20 @@
       <c r="F34">
         <v>19.9</v>
       </c>
+      <c r="I34">
+        <v>20</v>
+      </c>
+      <c r="J34">
+        <v>18.8</v>
+      </c>
+      <c r="K34">
+        <v>15.2</v>
+      </c>
+      <c r="L34">
+        <v>17.2</v>
+      </c>
       <c r="M34">
-        <v>17</v>
+        <v>16.1</v>
       </c>
       <c r="R34" s="2">
         <v>23471</v>
@@ -1761,6 +2052,21 @@
       <c r="F35">
         <v>19.6</v>
       </c>
+      <c r="H35">
+        <v>15.2</v>
+      </c>
+      <c r="I35">
+        <v>22.1</v>
+      </c>
+      <c r="J35">
+        <v>19.8</v>
+      </c>
+      <c r="K35">
+        <v>15.1</v>
+      </c>
+      <c r="L35">
+        <v>17.1</v>
+      </c>
       <c r="M35">
         <v>17.8</v>
       </c>
@@ -1788,17 +2094,23 @@
         <v>23.4</v>
       </c>
       <c r="E36">
-        <v>16.1</v>
-      </c>
-      <c r="F36">
-        <v>18.7</v>
-      </c>
-      <c r="H36">
-        <v>12.28</v>
+        <v>7.2</v>
+      </c>
+      <c r="I36">
+        <v>22.3</v>
+      </c>
+      <c r="J36">
+        <v>18.6</v>
+      </c>
+      <c r="K36">
+        <v>13.7</v>
       </c>
       <c r="M36">
         <v>18.1</v>
       </c>
+      <c r="P36" t="s">
+        <v>20</v>
+      </c>
       <c r="R36" s="2">
         <v>23473</v>
       </c>
@@ -1829,10 +2141,19 @@
         <v>19.8</v>
       </c>
       <c r="H37">
-        <v>19.3</v>
+        <v>14.5</v>
+      </c>
+      <c r="I37">
+        <v>24.3</v>
+      </c>
+      <c r="J37">
+        <v>21.2</v>
+      </c>
+      <c r="K37">
+        <v>14.4</v>
       </c>
       <c r="M37">
-        <v>19.3</v>
+        <v>18.5</v>
       </c>
       <c r="R37" s="2">
         <v>23474</v>
@@ -1863,8 +2184,17 @@
       <c r="F38">
         <v>18.1</v>
       </c>
-      <c r="H38">
-        <v>11.2</v>
+      <c r="I38">
+        <v>23.8</v>
+      </c>
+      <c r="J38">
+        <v>20.8</v>
+      </c>
+      <c r="K38">
+        <v>11.6</v>
+      </c>
+      <c r="L38">
+        <v>17.3</v>
       </c>
       <c r="M38">
         <v>17.8</v>
@@ -1898,8 +2228,14 @@
       <c r="F39">
         <v>19.6</v>
       </c>
-      <c r="H39">
-        <v>12.5</v>
+      <c r="I39">
+        <v>22.6</v>
+      </c>
+      <c r="J39">
+        <v>20.6</v>
+      </c>
+      <c r="K39">
+        <v>12.7</v>
       </c>
       <c r="M39">
         <v>18.4</v>
@@ -1931,14 +2267,17 @@
         <v>14.1</v>
       </c>
       <c r="F40">
-        <v>20.8</v>
-      </c>
-      <c r="H40">
-        <v>14.9</v>
+        <v>20.4</v>
       </c>
       <c r="I40">
         <v>25.7</v>
       </c>
+      <c r="J40">
+        <v>19.2</v>
+      </c>
+      <c r="K40">
+        <v>14.1</v>
+      </c>
       <c r="L40">
         <v>13.9</v>
       </c>
@@ -1974,11 +2313,20 @@
       <c r="F41">
         <v>19.1</v>
       </c>
+      <c r="H41">
+        <v>14.2</v>
+      </c>
+      <c r="I41">
+        <v>22.4</v>
+      </c>
       <c r="J41">
         <v>20.2</v>
       </c>
+      <c r="K41">
+        <v>14</v>
+      </c>
       <c r="L41">
-        <v>19</v>
+        <v>17.6</v>
       </c>
       <c r="M41">
         <v>14.1</v>
@@ -2004,17 +2352,26 @@
         <v>12</v>
       </c>
       <c r="D42">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="E42">
         <v>13</v>
       </c>
       <c r="F42">
-        <v>19.4</v>
+        <v>19.3</v>
+      </c>
+      <c r="H42">
+        <v>14.2</v>
+      </c>
+      <c r="I42">
+        <v>24.5</v>
       </c>
       <c r="J42">
         <v>19.4</v>
       </c>
+      <c r="K42">
+        <v>12.8</v>
+      </c>
       <c r="L42">
         <v>18.2</v>
       </c>
@@ -2042,19 +2399,31 @@
         <v>13</v>
       </c>
       <c r="D43">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="E43">
-        <v>12.54</v>
+        <v>12.4</v>
       </c>
       <c r="F43">
         <v>19.8</v>
       </c>
+      <c r="H43">
+        <v>12.6</v>
+      </c>
+      <c r="I43">
+        <v>23.4</v>
+      </c>
+      <c r="J43">
+        <v>19.2</v>
+      </c>
+      <c r="K43">
+        <v>12.4</v>
+      </c>
       <c r="L43">
         <v>17.5</v>
       </c>
       <c r="M43">
-        <v>17.7</v>
+        <v>17</v>
       </c>
       <c r="R43" s="2">
         <v>23480</v>
@@ -2080,11 +2449,23 @@
         <v>25.6</v>
       </c>
       <c r="E44">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="F44">
         <v>19.8</v>
       </c>
+      <c r="H44">
+        <v>16.5</v>
+      </c>
+      <c r="I44">
+        <v>20.7</v>
+      </c>
+      <c r="J44">
+        <v>16.6</v>
+      </c>
+      <c r="K44">
+        <v>16.5</v>
+      </c>
       <c r="L44">
         <v>18.1</v>
       </c>
@@ -2115,11 +2496,23 @@
         <v>25.8</v>
       </c>
       <c r="E45">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="F45">
         <v>19.5</v>
       </c>
+      <c r="H45">
+        <v>13.2</v>
+      </c>
+      <c r="I45">
+        <v>24.6</v>
+      </c>
+      <c r="J45">
+        <v>18.9</v>
+      </c>
+      <c r="K45">
+        <v>12.9</v>
+      </c>
       <c r="L45">
         <v>18.7</v>
       </c>
@@ -2159,11 +2552,17 @@
         <v>16.9</v>
       </c>
       <c r="I46">
-        <v>18.9</v>
+        <v>18.4</v>
+      </c>
+      <c r="J46">
+        <v>17</v>
       </c>
       <c r="K46">
         <v>16.5</v>
       </c>
+      <c r="L46">
+        <v>17.2</v>
+      </c>
       <c r="M46">
         <v>17</v>
       </c>
@@ -2199,6 +2598,12 @@
       <c r="I47">
         <v>18</v>
       </c>
+      <c r="J47">
+        <v>15.6</v>
+      </c>
+      <c r="L47">
+        <v>17.2</v>
+      </c>
       <c r="M47">
         <v>15.3</v>
       </c>
@@ -2231,9 +2636,21 @@
       <c r="F48">
         <v>18.9</v>
       </c>
+      <c r="H48">
+        <v>13.5</v>
+      </c>
       <c r="I48">
         <v>19.8</v>
       </c>
+      <c r="J48">
+        <v>19</v>
+      </c>
+      <c r="K48">
+        <v>13.4</v>
+      </c>
+      <c r="L48">
+        <v>17.6</v>
+      </c>
       <c r="M48">
         <v>17.6</v>
       </c>
@@ -2272,6 +2689,12 @@
       <c r="J49">
         <v>17.2</v>
       </c>
+      <c r="K49">
+        <v>14.3</v>
+      </c>
+      <c r="L49">
+        <v>17</v>
+      </c>
       <c r="M49">
         <v>17</v>
       </c>
@@ -2296,10 +2719,10 @@
         <v>20</v>
       </c>
       <c r="D50">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="E50">
-        <v>13.3</v>
+        <v>14</v>
       </c>
       <c r="F50">
         <v>18.5</v>
@@ -2307,6 +2730,15 @@
       <c r="I50">
         <v>23.6</v>
       </c>
+      <c r="J50">
+        <v>15.8</v>
+      </c>
+      <c r="K50">
+        <v>15</v>
+      </c>
+      <c r="L50">
+        <v>19</v>
+      </c>
       <c r="M50">
         <v>15.5</v>
       </c>
@@ -2330,9 +2762,33 @@
       <c r="C51">
         <v>21</v>
       </c>
+      <c r="D51">
+        <v>25.6</v>
+      </c>
+      <c r="E51">
+        <v>11.4</v>
+      </c>
+      <c r="F51">
+        <v>18.5</v>
+      </c>
+      <c r="G51">
+        <v>39.3</v>
+      </c>
+      <c r="H51">
+        <v>11.5</v>
+      </c>
+      <c r="I51">
+        <v>15</v>
+      </c>
       <c r="J51">
         <v>16.6</v>
       </c>
+      <c r="K51">
+        <v>11.1</v>
+      </c>
+      <c r="L51">
+        <v>14.8</v>
+      </c>
       <c r="M51">
         <v>16.2</v>
       </c>
@@ -2365,9 +2821,24 @@
       <c r="F52">
         <v>18.7</v>
       </c>
+      <c r="G52">
+        <v>7.2</v>
+      </c>
+      <c r="H52">
+        <v>14.3</v>
+      </c>
+      <c r="I52">
+        <v>21.2</v>
+      </c>
       <c r="J52">
         <v>17.8</v>
       </c>
+      <c r="K52">
+        <v>17.2</v>
+      </c>
+      <c r="L52">
+        <v>18.4</v>
+      </c>
       <c r="M52">
         <v>16.5</v>
       </c>
@@ -2391,8 +2862,32 @@
       <c r="C53">
         <v>23</v>
       </c>
+      <c r="D53">
+        <v>21.7</v>
+      </c>
+      <c r="E53">
+        <v>13.1</v>
+      </c>
+      <c r="F53">
+        <v>17.4</v>
+      </c>
+      <c r="G53">
+        <v>3.5</v>
+      </c>
+      <c r="H53">
+        <v>15.1</v>
+      </c>
+      <c r="I53">
+        <v>16.9</v>
+      </c>
       <c r="J53">
-        <v>16.9</v>
+        <v>16.4</v>
+      </c>
+      <c r="K53">
+        <v>15</v>
+      </c>
+      <c r="L53">
+        <v>15.8</v>
       </c>
       <c r="M53">
         <v>15.2</v>
@@ -2421,16 +2916,31 @@
         <v>24.1</v>
       </c>
       <c r="E54">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="F54">
         <v>18.1</v>
       </c>
+      <c r="G54">
+        <v>0.1</v>
+      </c>
+      <c r="H54">
+        <v>12.5</v>
+      </c>
+      <c r="I54">
+        <v>23.9</v>
+      </c>
       <c r="J54">
-        <v>18.9</v>
+        <v>18.4</v>
+      </c>
+      <c r="K54">
+        <v>12.3</v>
+      </c>
+      <c r="L54">
+        <v>18.3</v>
       </c>
       <c r="M54">
-        <v>16.5</v>
+        <v>15.6</v>
       </c>
       <c r="R54" s="2">
         <v>23491</v>
@@ -2461,9 +2971,24 @@
       <c r="F55">
         <v>19.5</v>
       </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>15</v>
+      </c>
+      <c r="I55">
+        <v>24</v>
+      </c>
       <c r="J55">
         <v>20.8</v>
       </c>
+      <c r="K55">
+        <v>14.6</v>
+      </c>
+      <c r="L55">
+        <v>17.6</v>
+      </c>
       <c r="M55">
         <v>17.2</v>
       </c>
@@ -2488,25 +3013,28 @@
         <v>26</v>
       </c>
       <c r="D56">
-        <v>25.1</v>
+        <v>25.9</v>
       </c>
       <c r="E56">
         <v>11.1</v>
       </c>
       <c r="F56">
-        <v>18.9</v>
-      </c>
-      <c r="H56">
-        <v>11.3</v>
+        <v>18.5</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
       </c>
       <c r="I56">
         <v>24.8</v>
       </c>
-      <c r="K56">
-        <v>9.9</v>
+      <c r="J56">
+        <v>21.5</v>
+      </c>
+      <c r="L56">
+        <v>18.4</v>
       </c>
       <c r="M56">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="R56" s="2">
         <v>23493</v>
@@ -2532,14 +3060,23 @@
         <v>26</v>
       </c>
       <c r="E57">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F57">
         <v>17.9</v>
       </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
       <c r="I57">
         <v>25.4</v>
       </c>
+      <c r="J57">
+        <v>22.3</v>
+      </c>
+      <c r="L57">
+        <v>17.6</v>
+      </c>
       <c r="M57">
         <v>17.3</v>
       </c>
@@ -2572,9 +3109,18 @@
       <c r="F58">
         <v>18.1</v>
       </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
       <c r="I58">
         <v>25.2</v>
       </c>
+      <c r="J58">
+        <v>21.7</v>
+      </c>
+      <c r="L58">
+        <v>17.2</v>
+      </c>
       <c r="M58">
         <v>16.2</v>
       </c>
@@ -2598,8 +3144,23 @@
       <c r="C59">
         <v>29</v>
       </c>
+      <c r="D59">
+        <v>26.9</v>
+      </c>
+      <c r="E59">
+        <v>10.4</v>
+      </c>
+      <c r="F59">
+        <v>18.7</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
       <c r="I59">
-        <v>26.7</v>
+        <v>26.1</v>
+      </c>
+      <c r="J59">
+        <v>22</v>
       </c>
       <c r="L59">
         <v>18.2</v>
@@ -2628,16 +3189,25 @@
         <v>30</v>
       </c>
       <c r="D60">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="E60">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="F60">
-        <v>19.2</v>
+        <v>19.3</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
       </c>
       <c r="I60">
         <v>24.8</v>
+      </c>
+      <c r="J60">
+        <v>21.4</v>
+      </c>
+      <c r="L60">
+        <v>17.8</v>
       </c>
       <c r="M60">
         <v>16</v>

--- a/results/04_final_refined_daily_hydroclimate_data/702/Daily_temperature_and_precipitation_station_702.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Daily_temperature_and_precipitation_station_702.xlsx
@@ -526,7 +526,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I2">
         <v>25.8</v>
@@ -540,6 +540,9 @@
       <c r="L2">
         <v>12.1</v>
       </c>
+      <c r="M2">
+        <v>18.3</v>
+      </c>
       <c r="R2" s="2">
         <v>23408</v>
       </c>
@@ -587,6 +590,9 @@
       <c r="L3">
         <v>18.6</v>
       </c>
+      <c r="M3">
+        <v>17.2</v>
+      </c>
       <c r="R3" s="2">
         <v>23409</v>
       </c>
@@ -684,6 +690,9 @@
       <c r="L5">
         <v>16.8</v>
       </c>
+      <c r="M5">
+        <v>16.8</v>
+      </c>
       <c r="R5" s="2">
         <v>23411</v>
       </c>
@@ -731,6 +740,9 @@
       <c r="L6">
         <v>18.4</v>
       </c>
+      <c r="M6">
+        <v>17.3</v>
+      </c>
       <c r="R6" s="2">
         <v>23412</v>
       </c>
@@ -760,6 +772,9 @@
       <c r="F7">
         <v>19</v>
       </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
       <c r="I7">
         <v>26.3</v>
       </c>
@@ -767,10 +782,10 @@
         <v>22.1</v>
       </c>
       <c r="L7">
-        <v>12.4</v>
+        <v>17.1</v>
       </c>
       <c r="M7">
-        <v>17.6</v>
+        <v>15.5</v>
       </c>
       <c r="R7" s="2">
         <v>23413</v>
@@ -801,6 +816,9 @@
       <c r="F8">
         <v>18.4</v>
       </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
       <c r="I8">
         <v>25.4</v>
       </c>
@@ -810,9 +828,6 @@
       <c r="L8">
         <v>15.5</v>
       </c>
-      <c r="M8">
-        <v>14.7</v>
-      </c>
       <c r="R8" s="2">
         <v>23414</v>
       </c>
@@ -842,6 +857,9 @@
       <c r="F9">
         <v>18.3</v>
       </c>
+      <c r="G9">
+        <v>0.5</v>
+      </c>
       <c r="I9">
         <v>18.9</v>
       </c>
@@ -883,6 +901,9 @@
       <c r="F10">
         <v>18.3</v>
       </c>
+      <c r="G10">
+        <v>16.7</v>
+      </c>
       <c r="I10">
         <v>14.9</v>
       </c>
@@ -892,9 +913,6 @@
       <c r="L10">
         <v>14.7</v>
       </c>
-      <c r="M10">
-        <v>15.2</v>
-      </c>
       <c r="R10" s="2">
         <v>23416</v>
       </c>
@@ -924,6 +942,9 @@
       <c r="F11">
         <v>18.5</v>
       </c>
+      <c r="G11">
+        <v>21.6</v>
+      </c>
       <c r="I11">
         <v>25.5</v>
       </c>
@@ -1027,9 +1048,6 @@
       <c r="J13">
         <v>21.2</v>
       </c>
-      <c r="K13">
-        <v>11</v>
-      </c>
       <c r="L13">
         <v>14.2</v>
       </c>
@@ -1077,9 +1095,6 @@
       <c r="J14">
         <v>22.2</v>
       </c>
-      <c r="K14">
-        <v>11</v>
-      </c>
       <c r="L14">
         <v>13.3</v>
       </c>
@@ -1119,7 +1134,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>13.1</v>
+        <v>17.6</v>
       </c>
       <c r="I15">
         <v>25.6</v>
@@ -1128,7 +1143,7 @@
         <v>19.8</v>
       </c>
       <c r="K15">
-        <v>13</v>
+        <v>17.4</v>
       </c>
       <c r="L15">
         <v>14.8</v>
@@ -1160,7 +1175,7 @@
         <v>25.2</v>
       </c>
       <c r="E16">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="F16">
         <v>18.7</v>
@@ -1354,7 +1369,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F20">
         <v>19.3</v>
@@ -1422,7 +1437,7 @@
         <v>10.5</v>
       </c>
       <c r="L21">
-        <v>15</v>
+        <v>18.7</v>
       </c>
       <c r="M21">
         <v>14.7</v>
@@ -1469,7 +1484,7 @@
         <v>10.2</v>
       </c>
       <c r="L22">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="M22">
         <v>17.6</v>
@@ -1560,7 +1575,7 @@
         <v>18.7</v>
       </c>
       <c r="K24">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="L24">
         <v>18.1</v>
@@ -1683,7 +1698,7 @@
         <v>26</v>
       </c>
       <c r="D27">
-        <v>26.9</v>
+        <v>26.92</v>
       </c>
       <c r="E27">
         <v>11</v>
@@ -1697,9 +1712,15 @@
       <c r="H27">
         <v>12.7</v>
       </c>
+      <c r="I27">
+        <v>26.6</v>
+      </c>
       <c r="J27">
         <v>21.7</v>
       </c>
+      <c r="K27">
+        <v>12.5</v>
+      </c>
       <c r="L27">
         <v>18</v>
       </c>
@@ -1791,9 +1812,15 @@
       <c r="H29">
         <v>8.800000000000001</v>
       </c>
+      <c r="I29">
+        <v>23.4</v>
+      </c>
       <c r="J29">
         <v>22</v>
       </c>
+      <c r="K29">
+        <v>8.6</v>
+      </c>
       <c r="L29">
         <v>17.4</v>
       </c>
@@ -1835,9 +1862,15 @@
       <c r="H30">
         <v>11.9</v>
       </c>
+      <c r="I30">
+        <v>26.6</v>
+      </c>
       <c r="J30">
         <v>22</v>
       </c>
+      <c r="K30">
+        <v>11.3</v>
+      </c>
       <c r="L30">
         <v>17.6</v>
       </c>
@@ -2052,9 +2085,6 @@
       <c r="F35">
         <v>19.6</v>
       </c>
-      <c r="H35">
-        <v>15.2</v>
-      </c>
       <c r="I35">
         <v>22.1</v>
       </c>
@@ -2094,7 +2124,10 @@
         <v>23.4</v>
       </c>
       <c r="E36">
-        <v>7.2</v>
+        <v>13.3</v>
+      </c>
+      <c r="F36">
+        <v>18.4</v>
       </c>
       <c r="I36">
         <v>22.3</v>
@@ -2108,9 +2141,6 @@
       <c r="M36">
         <v>18.1</v>
       </c>
-      <c r="P36" t="s">
-        <v>20</v>
-      </c>
       <c r="R36" s="2">
         <v>23473</v>
       </c>
@@ -2140,9 +2170,6 @@
       <c r="F37">
         <v>19.8</v>
       </c>
-      <c r="H37">
-        <v>14.5</v>
-      </c>
       <c r="I37">
         <v>24.3</v>
       </c>
@@ -2184,6 +2211,9 @@
       <c r="F38">
         <v>18.1</v>
       </c>
+      <c r="H38">
+        <v>11.7</v>
+      </c>
       <c r="I38">
         <v>23.8</v>
       </c>
@@ -2228,6 +2258,9 @@
       <c r="F39">
         <v>19.6</v>
       </c>
+      <c r="H39">
+        <v>12.5</v>
+      </c>
       <c r="I39">
         <v>22.6</v>
       </c>
@@ -2235,7 +2268,7 @@
         <v>20.6</v>
       </c>
       <c r="K39">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="M39">
         <v>18.4</v>
@@ -2313,6 +2346,9 @@
       <c r="F41">
         <v>19.1</v>
       </c>
+      <c r="G41">
+        <v>0.3</v>
+      </c>
       <c r="H41">
         <v>14.2</v>
       </c>
@@ -2360,6 +2396,9 @@
       <c r="F42">
         <v>19.3</v>
       </c>
+      <c r="G42">
+        <v>0.1</v>
+      </c>
       <c r="H42">
         <v>14.2</v>
       </c>
@@ -2369,9 +2408,6 @@
       <c r="J42">
         <v>19.4</v>
       </c>
-      <c r="K42">
-        <v>12.8</v>
-      </c>
       <c r="L42">
         <v>18.2</v>
       </c>
@@ -2407,6 +2443,9 @@
       <c r="F43">
         <v>19.8</v>
       </c>
+      <c r="G43">
+        <v>0.2</v>
+      </c>
       <c r="H43">
         <v>12.6</v>
       </c>
@@ -2416,9 +2455,6 @@
       <c r="J43">
         <v>19.2</v>
       </c>
-      <c r="K43">
-        <v>12.4</v>
-      </c>
       <c r="L43">
         <v>17.5</v>
       </c>
@@ -2454,6 +2490,9 @@
       <c r="F44">
         <v>19.8</v>
       </c>
+      <c r="G44">
+        <v>21.1</v>
+      </c>
       <c r="H44">
         <v>16.5</v>
       </c>
@@ -2501,6 +2540,9 @@
       <c r="F45">
         <v>19.5</v>
       </c>
+      <c r="G45">
+        <v>5.7</v>
+      </c>
       <c r="H45">
         <v>13.2</v>
       </c>
@@ -2510,9 +2552,6 @@
       <c r="J45">
         <v>18.9</v>
       </c>
-      <c r="K45">
-        <v>12.9</v>
-      </c>
       <c r="L45">
         <v>18.7</v>
       </c>
@@ -2548,24 +2587,21 @@
       <c r="F46">
         <v>19.3</v>
       </c>
+      <c r="G46">
+        <v>6.6</v>
+      </c>
       <c r="H46">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="I46">
         <v>18.4</v>
       </c>
-      <c r="J46">
-        <v>17</v>
-      </c>
       <c r="K46">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="L46">
         <v>17.2</v>
       </c>
-      <c r="M46">
-        <v>17</v>
-      </c>
       <c r="R46" s="2">
         <v>23483</v>
       </c>
@@ -2595,18 +2631,21 @@
       <c r="F47">
         <v>18.9</v>
       </c>
+      <c r="G47">
+        <v>17.7</v>
+      </c>
+      <c r="H47">
+        <v>9.9</v>
+      </c>
       <c r="I47">
         <v>18</v>
       </c>
-      <c r="J47">
-        <v>15.6</v>
+      <c r="K47">
+        <v>9.9</v>
       </c>
       <c r="L47">
         <v>17.2</v>
       </c>
-      <c r="M47">
-        <v>15.3</v>
-      </c>
       <c r="R47" s="2">
         <v>23484</v>
       </c>
@@ -2636,24 +2675,21 @@
       <c r="F48">
         <v>18.9</v>
       </c>
+      <c r="G48">
+        <v>13.2</v>
+      </c>
       <c r="H48">
         <v>13.5</v>
       </c>
       <c r="I48">
         <v>19.8</v>
       </c>
-      <c r="J48">
-        <v>19</v>
-      </c>
       <c r="K48">
         <v>13.4</v>
       </c>
       <c r="L48">
         <v>17.6</v>
       </c>
-      <c r="M48">
-        <v>17.6</v>
-      </c>
       <c r="R48" s="2">
         <v>23485</v>
       </c>
@@ -2683,6 +2719,9 @@
       <c r="F49">
         <v>18.7</v>
       </c>
+      <c r="G49">
+        <v>32.8</v>
+      </c>
       <c r="I49">
         <v>19.6</v>
       </c>
@@ -2727,20 +2766,17 @@
       <c r="F50">
         <v>18.5</v>
       </c>
+      <c r="G50">
+        <v>6.6</v>
+      </c>
       <c r="I50">
         <v>23.6</v>
       </c>
-      <c r="J50">
-        <v>15.8</v>
-      </c>
       <c r="K50">
         <v>15</v>
       </c>
       <c r="L50">
-        <v>19</v>
-      </c>
-      <c r="M50">
-        <v>15.5</v>
+        <v>16.8</v>
       </c>
       <c r="R50" s="2">
         <v>23487</v>
@@ -2763,19 +2799,16 @@
         <v>21</v>
       </c>
       <c r="D51">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="E51">
         <v>11.4</v>
       </c>
       <c r="F51">
-        <v>18.5</v>
-      </c>
-      <c r="G51">
-        <v>39.3</v>
+        <v>18.6</v>
       </c>
       <c r="H51">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="I51">
         <v>15</v>
@@ -2783,9 +2816,6 @@
       <c r="J51">
         <v>16.6</v>
       </c>
-      <c r="K51">
-        <v>11.1</v>
-      </c>
       <c r="L51">
         <v>14.8</v>
       </c>
@@ -2821,9 +2851,6 @@
       <c r="F52">
         <v>18.7</v>
       </c>
-      <c r="G52">
-        <v>7.2</v>
-      </c>
       <c r="H52">
         <v>14.3</v>
       </c>
@@ -2833,11 +2860,8 @@
       <c r="J52">
         <v>17.8</v>
       </c>
-      <c r="K52">
+      <c r="L52">
         <v>17.2</v>
-      </c>
-      <c r="L52">
-        <v>18.4</v>
       </c>
       <c r="M52">
         <v>16.5</v>
@@ -2862,18 +2886,12 @@
       <c r="C53">
         <v>23</v>
       </c>
-      <c r="D53">
-        <v>21.7</v>
-      </c>
       <c r="E53">
-        <v>13.1</v>
+        <v>15.1</v>
       </c>
       <c r="F53">
         <v>17.4</v>
       </c>
-      <c r="G53">
-        <v>3.5</v>
-      </c>
       <c r="H53">
         <v>15.1</v>
       </c>
@@ -2883,15 +2901,15 @@
       <c r="J53">
         <v>16.4</v>
       </c>
-      <c r="K53">
-        <v>15</v>
-      </c>
       <c r="L53">
         <v>15.8</v>
       </c>
       <c r="M53">
         <v>15.2</v>
       </c>
+      <c r="N53" t="s">
+        <v>20</v>
+      </c>
       <c r="R53" s="2">
         <v>23490</v>
       </c>
@@ -2921,9 +2939,6 @@
       <c r="F54">
         <v>18.1</v>
       </c>
-      <c r="G54">
-        <v>0.1</v>
-      </c>
       <c r="H54">
         <v>12.5</v>
       </c>
@@ -2933,9 +2948,6 @@
       <c r="J54">
         <v>18.4</v>
       </c>
-      <c r="K54">
-        <v>12.3</v>
-      </c>
       <c r="L54">
         <v>18.3</v>
       </c>
@@ -2971,9 +2983,6 @@
       <c r="F55">
         <v>19.5</v>
       </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
       <c r="H55">
         <v>15</v>
       </c>
@@ -3025,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>24.8</v>
+        <v>25.8</v>
       </c>
       <c r="J56">
         <v>21.5</v>
@@ -3148,7 +3157,7 @@
         <v>26.9</v>
       </c>
       <c r="E59">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="F59">
         <v>18.7</v>

--- a/results/04_final_refined_daily_hydroclimate_data/702/Daily_temperature_and_precipitation_station_702.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Daily_temperature_and_precipitation_station_702.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Year</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>Year_Num</t>
-  </si>
-  <si>
-    <t>Condition 1</t>
   </si>
 </sst>
 </file>
@@ -526,7 +523,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I2">
         <v>25.8</v>
@@ -540,9 +537,6 @@
       <c r="L2">
         <v>12.1</v>
       </c>
-      <c r="M2">
-        <v>18.3</v>
-      </c>
       <c r="R2" s="2">
         <v>23408</v>
       </c>
@@ -590,9 +584,6 @@
       <c r="L3">
         <v>18.6</v>
       </c>
-      <c r="M3">
-        <v>17.2</v>
-      </c>
       <c r="R3" s="2">
         <v>23409</v>
       </c>
@@ -690,9 +681,6 @@
       <c r="L5">
         <v>16.8</v>
       </c>
-      <c r="M5">
-        <v>16.8</v>
-      </c>
       <c r="R5" s="2">
         <v>23411</v>
       </c>
@@ -740,9 +728,6 @@
       <c r="L6">
         <v>18.4</v>
       </c>
-      <c r="M6">
-        <v>17.3</v>
-      </c>
       <c r="R6" s="2">
         <v>23412</v>
       </c>
@@ -772,9 +757,6 @@
       <c r="F7">
         <v>19</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
       <c r="I7">
         <v>26.3</v>
       </c>
@@ -782,7 +764,7 @@
         <v>22.1</v>
       </c>
       <c r="L7">
-        <v>17.1</v>
+        <v>12.4</v>
       </c>
       <c r="M7">
         <v>15.5</v>
@@ -816,9 +798,6 @@
       <c r="F8">
         <v>18.4</v>
       </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
       <c r="I8">
         <v>25.4</v>
       </c>
@@ -826,7 +805,7 @@
         <v>21.3</v>
       </c>
       <c r="L8">
-        <v>15.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R8" s="2">
         <v>23414</v>
@@ -857,9 +836,6 @@
       <c r="F9">
         <v>18.3</v>
       </c>
-      <c r="G9">
-        <v>0.5</v>
-      </c>
       <c r="I9">
         <v>18.9</v>
       </c>
@@ -901,9 +877,6 @@
       <c r="F10">
         <v>18.3</v>
       </c>
-      <c r="G10">
-        <v>16.7</v>
-      </c>
       <c r="I10">
         <v>14.9</v>
       </c>
@@ -942,9 +915,6 @@
       <c r="F11">
         <v>18.5</v>
       </c>
-      <c r="G11">
-        <v>21.6</v>
-      </c>
       <c r="I11">
         <v>25.5</v>
       </c>
@@ -1230,11 +1200,8 @@
       <c r="F17">
         <v>17.8</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
       <c r="H17">
-        <v>10.1</v>
+        <v>17</v>
       </c>
       <c r="I17">
         <v>24.7</v>
@@ -1243,7 +1210,7 @@
         <v>21.3</v>
       </c>
       <c r="K17">
-        <v>9.9</v>
+        <v>16.7</v>
       </c>
       <c r="L17">
         <v>17.2</v>
@@ -1280,9 +1247,6 @@
       <c r="F18">
         <v>17</v>
       </c>
-      <c r="G18">
-        <v>0.9</v>
-      </c>
       <c r="H18">
         <v>10.4</v>
       </c>
@@ -1298,6 +1262,9 @@
       <c r="L18">
         <v>16.2</v>
       </c>
+      <c r="M18">
+        <v>15.5</v>
+      </c>
       <c r="R18" s="2">
         <v>23424</v>
       </c>
@@ -1327,9 +1294,6 @@
       <c r="F19">
         <v>18.1</v>
       </c>
-      <c r="G19">
-        <v>7.1</v>
-      </c>
       <c r="H19">
         <v>12.4</v>
       </c>
@@ -1345,6 +1309,9 @@
       <c r="L19">
         <v>16</v>
       </c>
+      <c r="M19">
+        <v>16.7</v>
+      </c>
       <c r="R19" s="2">
         <v>23425</v>
       </c>
@@ -1374,9 +1341,6 @@
       <c r="F20">
         <v>19.3</v>
       </c>
-      <c r="G20">
-        <v>5.5</v>
-      </c>
       <c r="H20">
         <v>13.4</v>
       </c>
@@ -1392,6 +1356,9 @@
       <c r="L20">
         <v>18.6</v>
       </c>
+      <c r="M20">
+        <v>15.5</v>
+      </c>
       <c r="R20" s="2">
         <v>23426</v>
       </c>
@@ -1421,9 +1388,6 @@
       <c r="F21">
         <v>19.5</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
       <c r="H21">
         <v>10.9</v>
       </c>
@@ -1437,7 +1401,7 @@
         <v>10.5</v>
       </c>
       <c r="L21">
-        <v>18.7</v>
+        <v>15</v>
       </c>
       <c r="M21">
         <v>14.7</v>
@@ -1698,7 +1662,7 @@
         <v>26</v>
       </c>
       <c r="D27">
-        <v>26.92</v>
+        <v>26.9</v>
       </c>
       <c r="E27">
         <v>11</v>
@@ -1950,6 +1914,9 @@
       <c r="F32">
         <v>20.3</v>
       </c>
+      <c r="H32">
+        <v>14</v>
+      </c>
       <c r="I32">
         <v>21.3</v>
       </c>
@@ -2007,7 +1974,7 @@
         <v>14.2</v>
       </c>
       <c r="L33">
-        <v>17.9</v>
+        <v>15.9</v>
       </c>
       <c r="M33">
         <v>18</v>
@@ -2041,6 +2008,9 @@
       <c r="F34">
         <v>19.9</v>
       </c>
+      <c r="H34">
+        <v>15.4</v>
+      </c>
       <c r="I34">
         <v>20</v>
       </c>
@@ -2085,6 +2055,9 @@
       <c r="F35">
         <v>19.6</v>
       </c>
+      <c r="H35">
+        <v>15.2</v>
+      </c>
       <c r="I35">
         <v>22.1</v>
       </c>
@@ -2135,9 +2108,6 @@
       <c r="J36">
         <v>18.6</v>
       </c>
-      <c r="K36">
-        <v>13.7</v>
-      </c>
       <c r="M36">
         <v>18.1</v>
       </c>
@@ -2176,9 +2146,6 @@
       <c r="J37">
         <v>21.2</v>
       </c>
-      <c r="K37">
-        <v>14.4</v>
-      </c>
       <c r="M37">
         <v>18.5</v>
       </c>
@@ -2211,18 +2178,12 @@
       <c r="F38">
         <v>18.1</v>
       </c>
-      <c r="H38">
-        <v>11.7</v>
-      </c>
       <c r="I38">
         <v>23.8</v>
       </c>
       <c r="J38">
         <v>20.8</v>
       </c>
-      <c r="K38">
-        <v>11.6</v>
-      </c>
       <c r="L38">
         <v>17.3</v>
       </c>
@@ -2258,18 +2219,12 @@
       <c r="F39">
         <v>19.6</v>
       </c>
-      <c r="H39">
-        <v>12.5</v>
-      </c>
       <c r="I39">
         <v>22.6</v>
       </c>
       <c r="J39">
         <v>20.6</v>
       </c>
-      <c r="K39">
-        <v>12.4</v>
-      </c>
       <c r="M39">
         <v>18.4</v>
       </c>
@@ -2308,9 +2263,6 @@
       <c r="J40">
         <v>19.2</v>
       </c>
-      <c r="K40">
-        <v>14.1</v>
-      </c>
       <c r="L40">
         <v>13.9</v>
       </c>
@@ -2493,18 +2445,12 @@
       <c r="G44">
         <v>21.1</v>
       </c>
-      <c r="H44">
-        <v>16.5</v>
-      </c>
       <c r="I44">
         <v>20.7</v>
       </c>
       <c r="J44">
         <v>16.6</v>
       </c>
-      <c r="K44">
-        <v>16.5</v>
-      </c>
       <c r="L44">
         <v>18.1</v>
       </c>
@@ -2544,7 +2490,7 @@
         <v>5.7</v>
       </c>
       <c r="H45">
-        <v>13.2</v>
+        <v>16.7</v>
       </c>
       <c r="I45">
         <v>24.6</v>
@@ -2552,6 +2498,9 @@
       <c r="J45">
         <v>18.9</v>
       </c>
+      <c r="K45">
+        <v>16.2</v>
+      </c>
       <c r="L45">
         <v>18.7</v>
       </c>
@@ -2587,17 +2536,11 @@
       <c r="F46">
         <v>19.3</v>
       </c>
-      <c r="G46">
-        <v>6.6</v>
-      </c>
-      <c r="H46">
-        <v>16.5</v>
-      </c>
       <c r="I46">
         <v>18.4</v>
       </c>
       <c r="K46">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="L46">
         <v>17.2</v>
@@ -2631,17 +2574,14 @@
       <c r="F47">
         <v>18.9</v>
       </c>
-      <c r="G47">
-        <v>17.7</v>
-      </c>
       <c r="H47">
-        <v>9.9</v>
+        <v>15.8</v>
       </c>
       <c r="I47">
         <v>18</v>
       </c>
       <c r="K47">
-        <v>9.9</v>
+        <v>15.8</v>
       </c>
       <c r="L47">
         <v>17.2</v>
@@ -2675,9 +2615,6 @@
       <c r="F48">
         <v>18.9</v>
       </c>
-      <c r="G48">
-        <v>13.2</v>
-      </c>
       <c r="H48">
         <v>13.5</v>
       </c>
@@ -2719,24 +2656,15 @@
       <c r="F49">
         <v>18.7</v>
       </c>
-      <c r="G49">
-        <v>32.8</v>
-      </c>
       <c r="I49">
         <v>19.6</v>
       </c>
-      <c r="J49">
-        <v>17.2</v>
-      </c>
       <c r="K49">
         <v>14.3</v>
       </c>
       <c r="L49">
         <v>17</v>
       </c>
-      <c r="M49">
-        <v>17</v>
-      </c>
       <c r="R49" s="2">
         <v>23486</v>
       </c>
@@ -2766,9 +2694,6 @@
       <c r="F50">
         <v>18.5</v>
       </c>
-      <c r="G50">
-        <v>6.6</v>
-      </c>
       <c r="I50">
         <v>23.6</v>
       </c>
@@ -2799,19 +2724,16 @@
         <v>21</v>
       </c>
       <c r="D51">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="E51">
         <v>11.4</v>
       </c>
       <c r="F51">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="H51">
-        <v>11.6</v>
-      </c>
-      <c r="I51">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="J51">
         <v>16.6</v>
@@ -2886,8 +2808,11 @@
       <c r="C53">
         <v>23</v>
       </c>
+      <c r="D53">
+        <v>21.7</v>
+      </c>
       <c r="E53">
-        <v>15.1</v>
+        <v>13.1</v>
       </c>
       <c r="F53">
         <v>17.4</v>
@@ -2895,21 +2820,18 @@
       <c r="H53">
         <v>15.1</v>
       </c>
-      <c r="I53">
-        <v>16.9</v>
-      </c>
       <c r="J53">
         <v>16.4</v>
       </c>
+      <c r="K53">
+        <v>15</v>
+      </c>
       <c r="L53">
         <v>15.8</v>
       </c>
       <c r="M53">
         <v>15.2</v>
       </c>
-      <c r="N53" t="s">
-        <v>20</v>
-      </c>
       <c r="R53" s="2">
         <v>23490</v>
       </c>
@@ -2942,9 +2864,6 @@
       <c r="H54">
         <v>12.5</v>
       </c>
-      <c r="I54">
-        <v>23.9</v>
-      </c>
       <c r="J54">
         <v>18.4</v>
       </c>
@@ -2986,9 +2905,6 @@
       <c r="H55">
         <v>15</v>
       </c>
-      <c r="I55">
-        <v>24</v>
-      </c>
       <c r="J55">
         <v>20.8</v>
       </c>
@@ -3034,7 +2950,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>25.8</v>
+        <v>24.8</v>
       </c>
       <c r="J56">
         <v>21.5</v>
@@ -3084,7 +3000,7 @@
         <v>22.3</v>
       </c>
       <c r="L57">
-        <v>17.6</v>
+        <v>13.8</v>
       </c>
       <c r="M57">
         <v>17.3</v>

--- a/results/04_final_refined_daily_hydroclimate_data/702/Daily_temperature_and_precipitation_station_702.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Daily_temperature_and_precipitation_station_702.xlsx
@@ -535,7 +535,7 @@
         <v>9.1</v>
       </c>
       <c r="L2">
-        <v>12.1</v>
+        <v>16.8</v>
       </c>
       <c r="R2" s="2">
         <v>23408</v>
@@ -632,7 +632,7 @@
         <v>14.7</v>
       </c>
       <c r="M4">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="R4" s="2">
         <v>23410</v>
@@ -681,6 +681,9 @@
       <c r="L5">
         <v>16.8</v>
       </c>
+      <c r="M5">
+        <v>16.8</v>
+      </c>
       <c r="R5" s="2">
         <v>23411</v>
       </c>
@@ -728,6 +731,9 @@
       <c r="L6">
         <v>18.4</v>
       </c>
+      <c r="M6">
+        <v>17.3</v>
+      </c>
       <c r="R6" s="2">
         <v>23412</v>
       </c>
@@ -764,10 +770,7 @@
         <v>22.1</v>
       </c>
       <c r="L7">
-        <v>12.4</v>
-      </c>
-      <c r="M7">
-        <v>15.5</v>
+        <v>17.1</v>
       </c>
       <c r="R7" s="2">
         <v>23413</v>
@@ -805,7 +808,7 @@
         <v>21.3</v>
       </c>
       <c r="L8">
-        <v>9.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="R8" s="2">
         <v>23414</v>
@@ -845,9 +848,6 @@
       <c r="L9">
         <v>17.3</v>
       </c>
-      <c r="M9">
-        <v>16.8</v>
-      </c>
       <c r="R9" s="2">
         <v>23415</v>
       </c>
@@ -922,10 +922,7 @@
         <v>20.7</v>
       </c>
       <c r="L11">
-        <v>13.7</v>
-      </c>
-      <c r="M11">
-        <v>14.4</v>
+        <v>17.6</v>
       </c>
       <c r="R11" s="2">
         <v>23417</v>
@@ -968,11 +965,8 @@
       <c r="J12">
         <v>21</v>
       </c>
-      <c r="K12">
-        <v>14.5</v>
-      </c>
       <c r="L12">
-        <v>13.4</v>
+        <v>17.5</v>
       </c>
       <c r="M12">
         <v>15.5</v>
@@ -1018,11 +1012,14 @@
       <c r="J13">
         <v>21.2</v>
       </c>
+      <c r="K13">
+        <v>11</v>
+      </c>
       <c r="L13">
-        <v>14.2</v>
+        <v>18</v>
       </c>
       <c r="M13">
-        <v>16.4</v>
+        <v>17.8</v>
       </c>
       <c r="R13" s="2">
         <v>23419</v>
@@ -1065,8 +1062,11 @@
       <c r="J14">
         <v>22.2</v>
       </c>
+      <c r="K14">
+        <v>11</v>
+      </c>
       <c r="L14">
-        <v>13.3</v>
+        <v>18.1</v>
       </c>
       <c r="M14">
         <v>18.4</v>
@@ -1112,14 +1112,11 @@
       <c r="J15">
         <v>19.8</v>
       </c>
-      <c r="K15">
-        <v>17.4</v>
-      </c>
       <c r="L15">
-        <v>14.8</v>
+        <v>18.2</v>
       </c>
       <c r="M15">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="R15" s="2">
         <v>23421</v>
@@ -1166,7 +1163,7 @@
         <v>12.2</v>
       </c>
       <c r="L16">
-        <v>12.4</v>
+        <v>16.2</v>
       </c>
       <c r="M16">
         <v>15.6</v>
@@ -1210,13 +1207,13 @@
         <v>21.3</v>
       </c>
       <c r="K17">
-        <v>16.7</v>
+        <v>9.9</v>
       </c>
       <c r="L17">
         <v>17.2</v>
       </c>
       <c r="M17">
-        <v>14.8</v>
+        <v>16.9</v>
       </c>
       <c r="R17" s="2">
         <v>23423</v>
@@ -1401,10 +1398,10 @@
         <v>10.5</v>
       </c>
       <c r="L21">
-        <v>15</v>
+        <v>18.7</v>
       </c>
       <c r="M21">
-        <v>14.7</v>
+        <v>17.3</v>
       </c>
       <c r="R21" s="2">
         <v>23427</v>
@@ -1539,7 +1536,7 @@
         <v>18.7</v>
       </c>
       <c r="K24">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="L24">
         <v>18.1</v>
@@ -1736,7 +1733,7 @@
         <v>10.3</v>
       </c>
       <c r="L28">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="M28">
         <v>16.8</v>
@@ -1927,7 +1924,7 @@
         <v>13.9</v>
       </c>
       <c r="L32">
-        <v>17.9</v>
+        <v>18.9</v>
       </c>
       <c r="M32">
         <v>17.4</v>
@@ -1974,7 +1971,7 @@
         <v>14.2</v>
       </c>
       <c r="L33">
-        <v>15.9</v>
+        <v>17.9</v>
       </c>
       <c r="M33">
         <v>18</v>
@@ -2024,7 +2021,7 @@
         <v>17.2</v>
       </c>
       <c r="M34">
-        <v>16.1</v>
+        <v>17</v>
       </c>
       <c r="R34" s="2">
         <v>23471</v>
@@ -2068,7 +2065,7 @@
         <v>15.1</v>
       </c>
       <c r="L35">
-        <v>17.1</v>
+        <v>18.6</v>
       </c>
       <c r="M35">
         <v>17.8</v>
@@ -2147,7 +2144,7 @@
         <v>21.2</v>
       </c>
       <c r="M37">
-        <v>18.5</v>
+        <v>19.3</v>
       </c>
       <c r="R37" s="2">
         <v>23474</v>
@@ -2184,9 +2181,6 @@
       <c r="J38">
         <v>20.8</v>
       </c>
-      <c r="L38">
-        <v>17.3</v>
-      </c>
       <c r="M38">
         <v>17.8</v>
       </c>
@@ -2263,9 +2257,6 @@
       <c r="J40">
         <v>19.2</v>
       </c>
-      <c r="L40">
-        <v>13.9</v>
-      </c>
       <c r="M40">
         <v>17.3</v>
       </c>
@@ -2314,10 +2305,10 @@
         <v>14</v>
       </c>
       <c r="L41">
-        <v>17.6</v>
+        <v>19</v>
       </c>
       <c r="M41">
-        <v>14.1</v>
+        <v>16.7</v>
       </c>
       <c r="R41" s="2">
         <v>23478</v>
@@ -2364,7 +2355,7 @@
         <v>18.2</v>
       </c>
       <c r="M42">
-        <v>16.6</v>
+        <v>17.5</v>
       </c>
       <c r="R42" s="2">
         <v>23479</v>
@@ -2407,11 +2398,14 @@
       <c r="J43">
         <v>19.2</v>
       </c>
+      <c r="K43">
+        <v>12.4</v>
+      </c>
       <c r="L43">
         <v>17.5</v>
       </c>
       <c r="M43">
-        <v>17</v>
+        <v>17.7</v>
       </c>
       <c r="R43" s="2">
         <v>23480</v>
@@ -2498,9 +2492,6 @@
       <c r="J45">
         <v>18.9</v>
       </c>
-      <c r="K45">
-        <v>16.2</v>
-      </c>
       <c r="L45">
         <v>18.7</v>
       </c>
@@ -2625,7 +2616,7 @@
         <v>13.4</v>
       </c>
       <c r="L48">
-        <v>17.6</v>
+        <v>18.8</v>
       </c>
       <c r="R48" s="2">
         <v>23485</v>
@@ -2701,7 +2692,7 @@
         <v>15</v>
       </c>
       <c r="L50">
-        <v>16.8</v>
+        <v>19</v>
       </c>
       <c r="R50" s="2">
         <v>23487</v>
@@ -2783,7 +2774,7 @@
         <v>17.8</v>
       </c>
       <c r="L52">
-        <v>17.2</v>
+        <v>18.4</v>
       </c>
       <c r="M52">
         <v>16.5</v>
@@ -2820,6 +2811,9 @@
       <c r="H53">
         <v>15.1</v>
       </c>
+      <c r="I53">
+        <v>16.9</v>
+      </c>
       <c r="J53">
         <v>16.4</v>
       </c>
@@ -2867,11 +2861,14 @@
       <c r="J54">
         <v>18.4</v>
       </c>
+      <c r="K54">
+        <v>12.3</v>
+      </c>
       <c r="L54">
         <v>18.3</v>
       </c>
       <c r="M54">
-        <v>15.6</v>
+        <v>16.5</v>
       </c>
       <c r="R54" s="2">
         <v>23491</v>
@@ -3000,7 +2997,7 @@
         <v>22.3</v>
       </c>
       <c r="L57">
-        <v>13.8</v>
+        <v>17.6</v>
       </c>
       <c r="M57">
         <v>17.3</v>
